--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,16 +61,52 @@
     <t>2026-05-07</t>
   </si>
   <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1903 София, О5 Царско село</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
     <t>B9325TM</t>
   </si>
   <si>
+    <t>B6802BX</t>
+  </si>
+  <si>
     <t>78970156027720251</t>
   </si>
   <si>
+    <t>78970156027720277</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>13:05</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:05:00</t>
+  </si>
+  <si>
+    <t>17:42:00</t>
+  </si>
+  <si>
+    <t>11:39:00</t>
+  </si>
+  <si>
+    <t>3231541741 3231541741</t>
+  </si>
+  <si>
+    <t>3232107129 3232107129</t>
+  </si>
+  <si>
+    <t>3232518370 3232518370</t>
   </si>
   <si>
     <t>Общи литри по продукт / ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ</t>
@@ -491,24 +530,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -548,119 +589,213 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1903</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>29.58</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
         <v>1.43</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>42.3</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.54</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>45.55</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>33.03</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3">
+        <v>1.49</v>
+      </c>
+      <c r="I3" s="1">
+        <v>49.21</v>
+      </c>
+      <c r="J3">
+        <v>1.55</v>
+      </c>
+      <c r="K3" s="1">
+        <v>51.2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>29.28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4">
+        <v>1.49</v>
+      </c>
+      <c r="I4" s="1">
+        <v>43.63</v>
+      </c>
+      <c r="J4">
+        <v>1.57</v>
+      </c>
+      <c r="K4" s="1">
+        <v>45.97</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>116349</v>
+      <c r="N4" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6">
-        <v>29.58</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1.43</v>
-      </c>
-      <c r="E7" s="6">
-        <v>42.3</v>
-      </c>
-      <c r="F7" s="6">
-        <v>45.55</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="6">
+        <v>91.89</v>
+      </c>
+      <c r="C9" s="6">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.4707</v>
+      </c>
+      <c r="E9" s="6">
+        <v>135.14</v>
+      </c>
+      <c r="F9" s="6">
+        <v>142.72</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="9">
-        <v>29.58</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9">
-        <v>42.3</v>
-      </c>
-      <c r="F8" s="9">
-        <v>45.55</v>
+    <row r="10" spans="1:14">
+      <c r="A10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="9">
+        <v>91.89</v>
+      </c>
+      <c r="C10" s="9">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="9">
+        <v>135.14</v>
+      </c>
+      <c r="F10" s="9">
+        <v>142.72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
@@ -160,7 +160,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,12 +170,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -225,17 +219,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,64 +46,34 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1903 София, О5 Царско село</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>София Люлин</t>
+  </si>
+  <si>
+    <t>B6469TH</t>
   </si>
   <si>
     <t>B9325TM</t>
   </si>
   <si>
-    <t>B6802BX</t>
+    <t>78970156027720269</t>
   </si>
   <si>
     <t>78970156027720251</t>
   </si>
   <si>
-    <t>78970156027720277</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>13:05:00</t>
-  </si>
-  <si>
-    <t>17:42:00</t>
-  </si>
-  <si>
-    <t>11:39:00</t>
-  </si>
-  <si>
-    <t>3231541741 3231541741</t>
-  </si>
-  <si>
-    <t>3232107129 3232107129</t>
-  </si>
-  <si>
-    <t>3232518370 3232518370</t>
   </si>
   <si>
     <t>Общи литри по продукт / ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ</t>
@@ -524,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -533,17 +500,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -577,219 +541,148 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>38.95</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="H2">
+        <v>58.81</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J2">
+        <v>60.76</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>28.89</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="H3">
+        <v>43.62</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J3">
+        <v>45.07</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="6" spans="1:11">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2">
-        <v>29.58</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>1.43</v>
-      </c>
-      <c r="I2" s="1">
-        <v>42.3</v>
-      </c>
-      <c r="J2">
-        <v>1.54</v>
-      </c>
-      <c r="K2" s="1">
-        <v>45.55</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="B8" s="6">
+        <v>67.84</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.5099</v>
+      </c>
+      <c r="E8" s="6">
+        <v>102.43</v>
+      </c>
+      <c r="F8" s="6">
+        <v>105.83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3">
-        <v>33.03</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3">
-        <v>1.49</v>
-      </c>
-      <c r="I3" s="1">
-        <v>49.21</v>
-      </c>
-      <c r="J3">
-        <v>1.55</v>
-      </c>
-      <c r="K3" s="1">
-        <v>51.2</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>29.28</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4">
-        <v>1.49</v>
-      </c>
-      <c r="I4" s="1">
-        <v>43.63</v>
-      </c>
-      <c r="J4">
-        <v>1.57</v>
-      </c>
-      <c r="K4" s="1">
-        <v>45.97</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="6">
-        <v>91.89</v>
-      </c>
-      <c r="C9" s="6">
-        <v>3</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.4707</v>
-      </c>
-      <c r="E9" s="6">
-        <v>135.14</v>
-      </c>
-      <c r="F9" s="6">
-        <v>142.72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="9">
-        <v>91.89</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="9">
-        <v>135.14</v>
-      </c>
-      <c r="F10" s="9">
-        <v>142.72</v>
+      <c r="B9" s="9">
+        <v>67.84</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="9">
+        <v>102.43</v>
+      </c>
+      <c r="F9" s="9">
+        <v>105.83</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-08</t>
   </si>
   <si>
@@ -61,16 +70,16 @@
     <t>2026-06-23</t>
   </si>
   <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>София Люлин</t>
-  </si>
-  <si>
-    <t>Търговище</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1162 София Люлин П. Владигеров</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
   </si>
   <si>
     <t>B6469TH</t>
@@ -94,16 +103,31 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-08 16:54:45</t>
-  </si>
-  <si>
-    <t>2026-06-11 13:18:08</t>
-  </si>
-  <si>
-    <t>2026-06-20 07:52:15</t>
-  </si>
-  <si>
-    <t>2026-06-23 19:58:06</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>16:55:00</t>
+  </si>
+  <si>
+    <t>13:18:00</t>
+  </si>
+  <si>
+    <t>07:52:00</t>
+  </si>
+  <si>
+    <t>19:57:00</t>
+  </si>
+  <si>
+    <t>3233063743 3233063743</t>
+  </si>
+  <si>
+    <t>3233202229 3233202229</t>
+  </si>
+  <si>
+    <t>3233632581 3233632581</t>
+  </si>
+  <si>
+    <t>3233774964 3233774964</t>
   </si>
   <si>
     <t>Общи литри по продукт / ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ</t>
@@ -521,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -530,14 +554,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -571,150 +598,195 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>38.95</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2">
         <v>1.49</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>58.04</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.56</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>60.76</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>28.89</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3">
         <v>1.47</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>42.47</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.56</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>45.07</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>33.67</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4">
         <v>1.43</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>48.15</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.53</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>51.52</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
       </c>
       <c r="F5">
         <v>37.71</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5">
         <v>1.42</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>53.55</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.51</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>56.94</v>
       </c>
-      <c r="K5" t="s">
-        <v>29</v>
+      <c r="L5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -722,29 +794,29 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:14">
       <c r="A9" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:14">
       <c r="A10" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6">
         <v>139.22</v>
@@ -762,9 +834,9 @@
         <v>214.29</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:14">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B11" s="9">
         <v>139.22</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="51">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,16 +55,40 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
     <t>2026-07-11</t>
   </si>
   <si>
-    <t>София Царско Село</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1903 София, О5 Царско село</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1906 София, О5 Орион</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
   </si>
   <si>
     <t>B9325TM</t>
@@ -70,19 +97,58 @@
     <t>B6469TH</t>
   </si>
   <si>
+    <t>B6802BX</t>
+  </si>
+  <si>
     <t>78970156027720251</t>
   </si>
   <si>
     <t>78970156027720269</t>
   </si>
   <si>
+    <t>78970156027720277</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-01 09:59:17</t>
-  </si>
-  <si>
-    <t>2026-07-11 10:25:48</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:59:00</t>
+  </si>
+  <si>
+    <t>10:26:00</t>
+  </si>
+  <si>
+    <t>16:15:00</t>
+  </si>
+  <si>
+    <t>10:11:00</t>
+  </si>
+  <si>
+    <t>10:53:00</t>
+  </si>
+  <si>
+    <t>20:54:00</t>
+  </si>
+  <si>
+    <t>3234152114 3234152114</t>
+  </si>
+  <si>
+    <t>3234628622 3234628622</t>
+  </si>
+  <si>
+    <t>3234952806 3234952806</t>
+  </si>
+  <si>
+    <t>3234991997 3234991997</t>
+  </si>
+  <si>
+    <t>3235344975 3235344975</t>
+  </si>
+  <si>
+    <t>3235658483 3235658483</t>
   </si>
   <si>
     <t>Общи литри по продукт / ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ</t>
@@ -500,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -509,15 +575,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -554,154 +622,348 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>29.15</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2">
         <v>1.39</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>40.52</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.5</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>43.72</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>33.99</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3">
         <v>1.39</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>47.25</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.49</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>50.65</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="L3">
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4">
+        <v>33.33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4">
+        <v>1.4</v>
+      </c>
+      <c r="I4" s="1">
+        <v>46.66</v>
+      </c>
+      <c r="J4">
+        <v>1.5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50</v>
+      </c>
+      <c r="L4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3" t="s">
+      <c r="N4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>36.83</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5">
+        <v>1.41</v>
+      </c>
+      <c r="I5" s="1">
+        <v>51.93</v>
+      </c>
+      <c r="J5">
+        <v>1.52</v>
+      </c>
+      <c r="K5" s="1">
+        <v>55.98</v>
+      </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="6">
-        <v>63.14</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.3901</v>
-      </c>
-      <c r="E8" s="6">
-        <v>87.77</v>
-      </c>
-      <c r="F8" s="6">
-        <v>94.37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="9">
-        <v>63.14</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9">
-        <v>87.77</v>
-      </c>
-      <c r="F9" s="9">
-        <v>94.37</v>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6">
+        <v>35.14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>1.44</v>
+      </c>
+      <c r="I6" s="1">
+        <v>50.6</v>
+      </c>
+      <c r="J6">
+        <v>1.55</v>
+      </c>
+      <c r="K6" s="1">
+        <v>54.47</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>38.59</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="1">
+        <v>57.89</v>
+      </c>
+      <c r="J7">
+        <v>1.55</v>
+      </c>
+      <c r="K7" s="1">
+        <v>59.81</v>
+      </c>
+      <c r="L7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="6">
+        <v>207.03</v>
+      </c>
+      <c r="C12" s="6">
+        <v>6</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.4242</v>
+      </c>
+      <c r="E12" s="6">
+        <v>294.85</v>
+      </c>
+      <c r="F12" s="6">
+        <v>314.63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="9">
+        <v>207.03</v>
+      </c>
+      <c r="C13" s="9">
+        <v>6</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="9">
+        <v>294.85</v>
+      </c>
+      <c r="F13" s="9">
+        <v>314.63</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
@@ -175,7 +175,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -934,7 +934,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="7">
-        <v>1.4242</v>
+        <v>1.42419</v>
       </c>
       <c r="E12" s="6">
         <v>294.85</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="52">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -566,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -579,13 +582,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -628,274 +631,295 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2">
+        <v>29.153</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2">
+        <v>1.359</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.389</v>
+      </c>
+      <c r="J2">
+        <v>40.493517</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L2" s="1">
+        <v>43.7295</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3">
+        <v>33.993</v>
+      </c>
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3">
+        <v>1.359</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.389</v>
+      </c>
+      <c r="J3">
+        <v>47.216277</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L3" s="1">
+        <v>50.64957</v>
+      </c>
+      <c r="M3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4">
+        <v>33.333</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4">
+        <v>1.369</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J4">
+        <v>46.632867</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L4" s="1">
+        <v>49.9995</v>
+      </c>
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <v>36.829</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5">
+        <v>1.379</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.409</v>
+      </c>
+      <c r="J5">
+        <v>51.892061</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L5" s="1">
+        <v>55.98008</v>
+      </c>
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6">
+        <v>35.142</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6">
+        <v>1.401</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.441</v>
+      </c>
+      <c r="J6">
+        <v>50.639622</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L6" s="1">
+        <v>54.4701</v>
+      </c>
+      <c r="M6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C7" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D7" t="s">
         <v>31</v>
       </c>
-      <c r="F2">
-        <v>29.15</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="H2">
-        <v>1.39</v>
-      </c>
-      <c r="I2" s="1">
-        <v>40.52</v>
-      </c>
-      <c r="J2">
-        <v>1.5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>43.72</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="F7">
+        <v>38.587</v>
+      </c>
+      <c r="G7" t="s">
         <v>33</v>
       </c>
-      <c r="M2">
+      <c r="H7">
+        <v>1.459</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.499</v>
+      </c>
+      <c r="J7">
+        <v>57.841913</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L7" s="1">
+        <v>59.80985</v>
+      </c>
+      <c r="M7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3">
-        <v>33.99</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3">
-        <v>1.39</v>
-      </c>
-      <c r="I3" s="1">
-        <v>47.25</v>
-      </c>
-      <c r="J3">
-        <v>1.49</v>
-      </c>
-      <c r="K3" s="1">
-        <v>50.65</v>
-      </c>
-      <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4">
-        <v>33.33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4">
-        <v>1.4</v>
-      </c>
-      <c r="I4" s="1">
-        <v>46.66</v>
-      </c>
-      <c r="J4">
-        <v>1.5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>50</v>
-      </c>
-      <c r="L4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5">
-        <v>36.83</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5">
-        <v>1.41</v>
-      </c>
-      <c r="I5" s="1">
-        <v>51.93</v>
-      </c>
-      <c r="J5">
-        <v>1.52</v>
-      </c>
-      <c r="K5" s="1">
-        <v>55.98</v>
-      </c>
-      <c r="L5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6">
-        <v>35.14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6">
-        <v>1.44</v>
-      </c>
-      <c r="I6" s="1">
-        <v>50.6</v>
-      </c>
-      <c r="J6">
-        <v>1.55</v>
-      </c>
-      <c r="K6" s="1">
-        <v>54.47</v>
-      </c>
-      <c r="L6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7">
-        <v>38.59</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7">
-        <v>1.5</v>
-      </c>
-      <c r="I7" s="1">
-        <v>57.89</v>
-      </c>
-      <c r="J7">
-        <v>1.55</v>
-      </c>
-      <c r="K7" s="1">
-        <v>59.81</v>
-      </c>
-      <c r="L7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -903,62 +927,62 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6">
-        <v>207.03</v>
+        <v>207.037</v>
       </c>
       <c r="C12" s="6">
         <v>6</v>
       </c>
       <c r="D12" s="7">
-        <v>1.42419</v>
+        <v>1.423496</v>
       </c>
       <c r="E12" s="6">
-        <v>294.85</v>
+        <v>294.72</v>
       </c>
       <c r="F12" s="6">
-        <v>314.63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>314.64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="9">
-        <v>207.03</v>
+        <v>207.037</v>
       </c>
       <c r="C13" s="9">
         <v>6</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="9">
-        <v>294.85</v>
+        <v>294.72</v>
       </c>
       <c r="F13" s="9">
-        <v>314.63</v>
+        <v>314.64</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ/ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="51">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -177,8 +174,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -271,10 +268,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -569,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -582,13 +579,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -631,295 +628,274 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>29.153</v>
       </c>
       <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2">
+        <v>1.389</v>
+      </c>
+      <c r="I2" s="1">
+        <v>40.494</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>43.73</v>
+      </c>
+      <c r="L2" t="s">
         <v>33</v>
       </c>
-      <c r="H2">
-        <v>1.359</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.389</v>
-      </c>
-      <c r="J2">
-        <v>40.493517</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
-        <v>43.7295</v>
-      </c>
-      <c r="M2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>33.993</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I3" s="1">
-        <v>1.389</v>
+        <v>47.216</v>
       </c>
       <c r="J3">
-        <v>47.216277</v>
+        <v>1.49</v>
       </c>
       <c r="K3" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L3" s="1">
-        <v>50.64957</v>
-      </c>
-      <c r="M3" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3">
+        <v>50.65</v>
+      </c>
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>33.333</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H4">
-        <v>1.369</v>
+        <v>1.399</v>
       </c>
       <c r="I4" s="1">
-        <v>1.399</v>
+        <v>46.633</v>
       </c>
       <c r="J4">
-        <v>46.632867</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L4" s="1">
-        <v>49.9995</v>
-      </c>
-      <c r="M4" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4">
+        <v>50</v>
+      </c>
+      <c r="L4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
         <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
       </c>
       <c r="F5">
         <v>36.829</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H5">
-        <v>1.379</v>
+        <v>1.409</v>
       </c>
       <c r="I5" s="1">
-        <v>1.409</v>
+        <v>51.892</v>
       </c>
       <c r="J5">
-        <v>51.892061</v>
+        <v>1.52</v>
       </c>
       <c r="K5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L5" s="1">
-        <v>55.98008</v>
-      </c>
-      <c r="M5" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5">
+        <v>55.98</v>
+      </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
       </c>
       <c r="F6">
         <v>35.142</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H6">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I6" s="1">
-        <v>1.441</v>
+        <v>50.64</v>
       </c>
       <c r="J6">
-        <v>50.639622</v>
+        <v>1.55</v>
       </c>
       <c r="K6" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L6" s="1">
-        <v>54.4701</v>
-      </c>
-      <c r="M6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N6">
+        <v>54.47</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
         <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
       </c>
       <c r="F7">
         <v>38.587</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H7">
-        <v>1.459</v>
+        <v>1.499</v>
       </c>
       <c r="I7" s="1">
-        <v>1.499</v>
+        <v>57.842</v>
       </c>
       <c r="J7">
-        <v>57.841913</v>
+        <v>1.55</v>
       </c>
       <c r="K7" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L7" s="1">
-        <v>59.80985</v>
-      </c>
-      <c r="M7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7">
+        <v>59.81</v>
+      </c>
+      <c r="L7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
+      <c r="N7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -927,49 +903,49 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="E11" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="6">
         <v>207.037</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>6</v>
       </c>
       <c r="D12" s="7">
-        <v>1.423496</v>
-      </c>
-      <c r="E12" s="6">
-        <v>294.72</v>
-      </c>
-      <c r="F12" s="6">
+        <v>1.423</v>
+      </c>
+      <c r="E12" s="7">
+        <v>294.717</v>
+      </c>
+      <c r="F12" s="7">
         <v>314.64</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="9">
         <v>207.037</v>
@@ -979,7 +955,7 @@
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="9">
-        <v>294.72</v>
+        <v>294.717</v>
       </c>
       <c r="F13" s="9">
         <v>314.64</v>
